--- a/docs/SmartPlaze_Test_Scenarios.xlsx
+++ b/docs/SmartPlaze_Test_Scenarios.xlsx
@@ -1304,7 +1304,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1344,7 +1343,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Cannot be run until the named key is configured (Resend, K-Pay, Google URI, Anthropic).</t>
+          <t>Cannot be run until the named key is configured (K-Pay live keys, Google redirect URI).</t>
         </is>
       </c>
     </row>
@@ -1360,8 +1359,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="26.25" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -1754,7 +1751,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
@@ -2924,12 +2920,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Chat assistant without API key</t>
+          <t>Chat assistant in built-in mode (no Gemini key)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>ANTHROPIC_API_KEY empty</t>
+          <t>GEMINI_API_KEY empty (or Gemini quota/outage)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2937,22 +2933,24 @@
           <t>1.
 Click the round chat button.
 2.
-Send a message.</t>
+Ask "sofa under 400000", then "je cherche un canapé".
+3.
+Ask "how does escrow work?" and "talk to a person".</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>hello</t>
+          <t>sofa under 400000</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Widget shows the offline notice and shortcut chips (find a product, track order, escrow…); chips navigate correctly.</t>
+          <t>Status shows Online; replies list real listings as cards (budget respected, French understood); escrow answer links to /how-it-works; "Talk to a person" opens WhatsApp +237678240437. Footer note says quick answers from live listings.</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Blocked (needs provider key)</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -2977,12 +2975,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Chat assistant with API key</t>
+          <t>Chat assistant with Gemini (gemini-2.5-flash)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>ANTHROPIC_API_KEY set</t>
+          <t>GEMINI_API_KEY set (same key as ELIZFLOW)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3000,7 +2998,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Answer lists real listings with links; order status answer matches the account.</t>
+          <t>Natural-language answers from Gemini listing real products as cards with links; order status matches the account; footer note says answers are AI-generated. If Gemini fails, the chat silently falls back to built-in answers.</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -8222,7 +8220,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -8377,7 +8374,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="16.85" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -8477,7 +8473,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ANTHROPIC_API_KEY not set: the chat widget is in offline mode (shortcut chips).</t>
+          <t>GEMINI_API_KEY set on the server (same key and model as ELIZFLOW). Without it, the chat answers in built-in mode.</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>

--- a/docs/SmartPlaze_Test_Scenarios.xlsx
+++ b/docs/SmartPlaze_Test_Scenarios.xlsx
@@ -1304,6 +1304,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1359,6 +1360,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="26.25" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -1751,6 +1754,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
@@ -3298,12 +3302,12 @@
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>1.
-Register with test@smartmarket.dev.</t>
+Register with test@smartplaze.com.</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>test@smartmarket.dev</t>
+          <t>test@smartplaze.com</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3354,7 +3358,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>buyer@smartmarket.dev / BuyerPass123</t>
+          <t>buyer@smartplaze.com / BuyerPass123</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -3405,7 +3409,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>buyer@smartmarket.dev / wrong</t>
+          <t>buyer@smartplaze.com / wrong</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -7662,7 +7666,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>tech.elite@smartmarket.dev / Seller123! buying Smart Trust items</t>
+          <t>tech.elite@smartplaze.com / Seller123! buying Smart Trust items</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8098,7 +8102,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>tech.elite@smartmarket.dev</t>
+          <t>tech.elite@smartplaze.com</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8220,6 +8224,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -8250,7 +8255,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>test@smartmarket.dev</t>
+          <t>test@smartplaze.com</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -8272,7 +8277,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>accountant@smartmarket.dev</t>
+          <t>accountant@smartplaze.com</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -8294,7 +8299,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>cs@smartmarket.dev</t>
+          <t>cs@smartplaze.com</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -8316,7 +8321,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>buyer@smartmarket.dev</t>
+          <t>buyer@smartplaze.com</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -8338,7 +8343,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>smarttrust@smartmarket.dev</t>
+          <t>smarttrust@smartplaze.com</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -8360,7 +8365,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>tech.elite@smartmarket.dev</t>
+          <t>tech.elite@smartplaze.com</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -8374,6 +8379,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="16.85" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
